--- a/src/test/output_test/Specific_Regions/Region_100_500_0/Stats_specific_100_500_0.xlsx
+++ b/src/test/output_test/Specific_Regions/Region_100_500_0/Stats_specific_100_500_0.xlsx
@@ -522,49 +522,49 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>8715</v>
+        <v>8078</v>
       </c>
       <c r="G2">
-        <v>24956.16060755858</v>
+        <v>24234</v>
       </c>
       <c r="H2">
-        <v>24.95616060755858</v>
+        <v>24.234</v>
       </c>
       <c r="I2">
         <v>101</v>
       </c>
       <c r="J2">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="K2">
-        <v>123.6477337923121</v>
+        <v>123.9918296608071</v>
       </c>
       <c r="L2">
         <v>101</v>
       </c>
       <c r="M2">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="N2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O2">
-        <v>24.45606207471335</v>
+        <v>24.63130821710377</v>
       </c>
       <c r="P2">
-        <v>3.147251119997509</v>
+        <v>3.255185975814687</v>
       </c>
       <c r="Q2">
-        <v>22.35416777579665</v>
+        <v>26.09502884311661</v>
       </c>
       <c r="R2">
         <v>103</v>
@@ -573,7 +573,7 @@
         <v>107</v>
       </c>
       <c r="T2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U2">
         <v>154</v>
